--- a/code/data/numbers/lcdm-fixed.xlsx
+++ b/code/data/numbers/lcdm-fixed.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/852b2bada49559ee/code_final/data/numbers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\28943\OneDrive\NeutrinoForecast_J-PAS_PFS\code\data\numbers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_085D38BF95627E0F6235547658E5B6BB83C38146" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D01702B4-BA88-4F4E-8822-3ADA275606F5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2715183B-C111-484A-8AA8-EEF279192D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="437" windowWidth="18720" windowHeight="11434" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -64,23 +69,25 @@
     <t>DESI Multitracer</t>
   </si>
   <si>
+    <t>CMB + DESI Multitracer</t>
+  </si>
+  <si>
     <t>CMB + J-PAS Multitracer
 + PFS ELG</t>
-  </si>
-  <si>
-    <t>CMB + DESI Multitracer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="177" formatCode="0.0000_ "/>
-    <numFmt numFmtId="178" formatCode="0.000_ "/>
-    <numFmt numFmtId="179" formatCode="0.00000_ "/>
+  <numFmts count="4">
+    <numFmt numFmtId="178" formatCode="0.0000_);[Red]\(0.0000\)"/>
+    <numFmt numFmtId="179" formatCode="0.0000_ "/>
+    <numFmt numFmtId="180" formatCode="0.00000_ "/>
+    <numFmt numFmtId="181" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +107,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -137,15 +151,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -154,6 +164,17 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -459,30 +480,30 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.07421875" customWidth="1"/>
-    <col min="2" max="3" width="9.23046875" style="3"/>
-    <col min="4" max="4" width="9.23046875" style="7"/>
-    <col min="5" max="6" width="9.23046875" style="3"/>
-    <col min="7" max="7" width="9.23046875" style="5"/>
+    <col min="2" max="2" width="11.765625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.69140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="23" style="7" customWidth="1"/>
+    <col min="5" max="6" width="9.23046875" style="5"/>
+    <col min="7" max="7" width="11.4609375" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
@@ -491,22 +512,22 @@
         <v>6</v>
       </c>
       <c r="B2" s="3">
-        <v>6.9868713740317556E-3</v>
-      </c>
-      <c r="C2" s="3">
-        <v>9.2442038102615847E-3</v>
+        <v>6.7678259046500136E-3</v>
+      </c>
+      <c r="C2" s="5">
+        <v>8.9423057791772308E-3</v>
       </c>
       <c r="D2" s="7">
-        <v>1.008187376787942E-3</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1.0340888447274949E-2</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1.9903958078627648E-3</v>
-      </c>
-      <c r="G2" s="5">
-        <v>5.167925246854109E-2</v>
+        <v>9.7282085875472261E-4</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1.008495786700893E-2</v>
+      </c>
+      <c r="F2" s="5">
+        <v>1.9274020943380709E-3</v>
+      </c>
+      <c r="G2" s="9">
+        <v>5.0220274885649903E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -516,19 +537,19 @@
       <c r="B3" s="3">
         <v>1.317570336685547E-2</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>1.4649366813498141E-2</v>
       </c>
       <c r="D3" s="7">
         <v>5.7139750688055928E-3</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="5">
         <v>2.0619412062340699E-2</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="5">
         <v>2.634983164942465E-2</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="9">
         <v>0.26877506789347239</v>
       </c>
     </row>
@@ -539,19 +560,19 @@
       <c r="B4" s="3">
         <v>1.9501174379150062E-2</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>2.283188864963992E-2</v>
       </c>
       <c r="D4" s="7">
         <v>8.1056911329151493E-3</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="5">
         <v>3.4890979348592713E-2</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="5">
         <v>4.7364442554428121E-2</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="9">
         <v>0.3744605365787963</v>
       </c>
     </row>
@@ -562,19 +583,19 @@
       <c r="B5" s="3">
         <v>1.574034129122432E-2</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>3.1036331171435019E-2</v>
       </c>
       <c r="D5" s="7">
         <v>8.8135401892936571E-3</v>
       </c>
-      <c r="E5" s="3">
-        <v>4.338359083307361E-2</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5" s="5">
+        <v>4.3383590833073638E-2</v>
+      </c>
+      <c r="F5" s="5">
         <v>4.6786307794190733E-2</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="9">
         <v>0.3560004074318136</v>
       </c>
     </row>
@@ -583,22 +604,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="3">
-        <v>1.516049916220962E-2</v>
-      </c>
-      <c r="C6" s="3">
+        <v>1.516049916220959E-2</v>
+      </c>
+      <c r="C6" s="5">
         <v>1.3098281949801191E-2</v>
       </c>
       <c r="D6" s="7">
         <v>6.1850358767790844E-3</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="5">
         <v>3.7094135841929853E-2</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="5">
         <v>4.6400055037948973E-2</v>
       </c>
-      <c r="G6" s="5">
-        <v>0.55286480182355957</v>
+      <c r="G6" s="9">
+        <v>0.55286480182355935</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -608,43 +629,43 @@
       <c r="B7" s="3">
         <v>7.6712772356614467E-3</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>7.3444270537942422E-3</v>
       </c>
       <c r="D7" s="7">
         <v>3.2860095446189249E-3</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="5">
         <v>1.4946688121633611E-2</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="5">
         <v>1.5482998462272029E-2</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="9">
         <v>0.2045772893745357</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="3">
-        <v>6.3199540492266254E-3</v>
-      </c>
-      <c r="C8" s="3">
-        <v>4.8257159633511813E-3</v>
+        <v>6.3199540492265777E-3</v>
+      </c>
+      <c r="C8" s="5">
+        <v>4.8257159633512247E-3</v>
       </c>
       <c r="D8" s="7">
-        <v>2.6372563306273989E-3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1.3440724826967969E-2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1.183464788465389E-2</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0.18360734812713639</v>
+        <v>2.6372563306273872E-3</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1.3440724826967881E-2</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1.183464788465385E-2</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0.1836073481271345</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -654,70 +675,71 @@
       <c r="B9" s="3">
         <v>5.7416382859245387E-3</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>3.8030884766847772E-3</v>
       </c>
       <c r="D9" s="7">
         <v>2.2845367708237111E-3</v>
       </c>
-      <c r="E9" s="3">
-        <v>1.384992283383229E-2</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E9" s="5">
+        <v>1.3849922833832261E-2</v>
+      </c>
+      <c r="F9" s="5">
         <v>1.808473796893521E-2</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="9">
         <v>0.21454506066141121</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
+    <row r="10" spans="1:7" ht="84.9" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="B10" s="3">
-        <v>1.593418848633655E-3</v>
-      </c>
-      <c r="C10" s="3">
-        <v>2.0802611419927421E-3</v>
+        <v>1.586664217319837E-3</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2.0725149201610469E-3</v>
       </c>
       <c r="D10" s="7">
-        <v>2.4846004512768679E-4</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3.825080739405197E-3</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1.525099267315831E-3</v>
-      </c>
-      <c r="G10" s="5">
-        <v>1.6785642416613129E-2</v>
+        <v>2.4944312586065422E-4</v>
+      </c>
+      <c r="E10" s="5">
+        <v>3.8429950212388068E-3</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1.502564248440219E-3</v>
+      </c>
+      <c r="G10" s="9">
+        <v>1.6821883753656629E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="3">
-        <v>1.342539591957658E-3</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1.784371951854175E-3</v>
+        <v>1.34147722951146E-3</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1.7807374282386879E-3</v>
       </c>
       <c r="D11" s="7">
-        <v>2.0315873538660461E-4</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2.7995043778335201E-3</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1.510370517284951E-3</v>
-      </c>
-      <c r="G11" s="5">
-        <v>1.3089943415041929E-2</v>
+        <v>2.038398930784218E-4</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2.8053826624685409E-3</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1.4881744340349309E-3</v>
+      </c>
+      <c r="G11" s="9">
+        <v>1.3090393461134111E-2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>